--- a/Repasse.xlsx
+++ b/Repasse.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{274C214E-40D9-447F-87AF-4DE964E1D13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9264532-DF2B-4A47-B8CE-5028022926F8}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{274C214E-40D9-447F-87AF-4DE964E1D13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89ACB533-3C7C-46F6-BE7D-70915675FAB8}"/>
   <bookViews>
-    <workbookView xWindow="-24975" yWindow="1440" windowWidth="17280" windowHeight="8880" xr2:uid="{7312FC1A-F563-4D09-A125-E1314866FDBA}"/>
+    <workbookView xWindow="-25650" yWindow="-510" windowWidth="17280" windowHeight="8880" xr2:uid="{7312FC1A-F563-4D09-A125-E1314866FDBA}"/>
   </bookViews>
   <sheets>
     <sheet name="REPASSE" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPASSE!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPASSE!$A$1:$H$148</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="44">
   <si>
     <t xml:space="preserve">VIGNOLI </t>
   </si>
@@ -565,7 +565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB65D39-B272-4BDB-AA66-04D7F2E886E7}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -604,7 +604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -633,7 +633,7 @@
         <v>491.92350999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -662,7 +662,7 @@
         <v>3368.8382079999997</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -691,7 +691,7 @@
         <v>133.927808</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -720,7 +720,7 @@
         <v>3311.440576</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -749,7 +749,7 @@
         <v>13.29523</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -778,7 +778,7 @@
         <v>81.738130000000012</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -807,7 +807,7 @@
         <v>1738.0956449999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -836,7 +836,7 @@
         <v>170.28121499999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -865,7 +865,7 @@
         <v>143.49408</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -894,7 +894,7 @@
         <v>946.00675000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -981,7 +981,7 @@
         <v>1023.5911039999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>1023.5911039999999</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>2663.21551</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>2357.7871019999998</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>7158.0888959999993</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>2</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>6775.8628340000005</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>2</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>38</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>508.28687000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>38</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>2971.0826879999995</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>38</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>132.92083200000002</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>38</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>4015.8202880000003</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>38</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>170.178944</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>38</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>146.78248600000003</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>38</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>1068.6218119999999</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>38</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>13.090688</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>38</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>1057.946293</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>38</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>3703.6577280000006</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>38</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>614.75884800000006</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>38</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>727.19401199999993</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>38</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>2508.959374</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>2</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>2559.245238</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>2</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>6741.2008319999995</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>2</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>4340.3183039999994</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>2</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>3974.1881240000007</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>38</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>562.4905</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>38</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>3495.7171840000005</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>38</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>131.41036799999998</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>38</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>4499.6722560000007</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>38</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>126.37548799999999</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>38</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>1713.5427379999999</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>38</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>98.180160000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>38</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>727.71323400000006</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>38</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>980.794624</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>38</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>38</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>520.00083299999994</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>2</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>2484.9964920000002</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>2</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>7199.3749120000002</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>2</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>5746.5602880000006</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>2</v>
       </c>
@@ -4391,19 +4391,19 @@
         <v>5308.76</v>
       </c>
       <c r="F132" s="1">
-        <f t="shared" ref="F132:F148" si="6">E132*0.1</f>
+        <f t="shared" ref="F132:F150" si="6">E132*0.1</f>
         <v>530.87600000000009</v>
       </c>
       <c r="G132" s="1">
-        <f t="shared" ref="G132:G148" si="7">E132*0.1133</f>
+        <f t="shared" ref="G132:G150" si="7">E132*0.1133</f>
         <v>601.48250800000005</v>
       </c>
       <c r="H132" s="1">
-        <f t="shared" ref="H132:H148" si="8">E132-F132-G132</f>
+        <f t="shared" ref="H132:H150" si="8">E132-F132-G132</f>
         <v>4176.401492</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>38</v>
       </c>
@@ -4867,13 +4867,446 @@
         <v>5068.7080999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E149" s="1">
+        <v>556.4</v>
+      </c>
+      <c r="F149" s="1">
+        <f t="shared" si="6"/>
+        <v>55.64</v>
+      </c>
+      <c r="G149" s="1">
+        <f t="shared" si="7"/>
+        <v>63.040119999999995</v>
+      </c>
+      <c r="H149" s="1">
+        <f t="shared" si="8"/>
+        <v>437.71987999999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D150" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E150" s="1">
+        <v>2684.16</v>
+      </c>
+      <c r="F150" s="1">
+        <f t="shared" si="6"/>
+        <v>268.416</v>
+      </c>
+      <c r="G150" s="1">
+        <f t="shared" si="7"/>
+        <v>304.11532799999998</v>
+      </c>
+      <c r="H150" s="1">
+        <f t="shared" si="8"/>
+        <v>2111.6286719999998</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D151" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E151" s="1">
+        <v>182.4</v>
+      </c>
+      <c r="F151" s="1">
+        <f t="shared" ref="F151:F163" si="9">E151*0.1</f>
+        <v>18.240000000000002</v>
+      </c>
+      <c r="G151" s="1">
+        <f t="shared" ref="G151:G163" si="10">E151*0.1133</f>
+        <v>20.66592</v>
+      </c>
+      <c r="H151" s="1">
+        <f t="shared" ref="H151:H163" si="11">E151-F151-G151</f>
+        <v>143.49408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D152" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5458.56</v>
+      </c>
+      <c r="F152" s="1">
+        <f t="shared" si="9"/>
+        <v>545.85600000000011</v>
+      </c>
+      <c r="G152" s="1">
+        <f t="shared" si="10"/>
+        <v>618.45484800000008</v>
+      </c>
+      <c r="H152" s="1">
+        <f t="shared" si="11"/>
+        <v>4294.2491520000003</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D153" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E153" s="1">
+        <v>158.72</v>
+      </c>
+      <c r="F153" s="1">
+        <f t="shared" si="9"/>
+        <v>15.872</v>
+      </c>
+      <c r="G153" s="1">
+        <f t="shared" si="10"/>
+        <v>17.982976000000001</v>
+      </c>
+      <c r="H153" s="1">
+        <f t="shared" si="11"/>
+        <v>124.86502400000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D154" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E154" s="1">
+        <v>2533.6999999999998</v>
+      </c>
+      <c r="F154" s="1">
+        <f t="shared" si="9"/>
+        <v>253.37</v>
+      </c>
+      <c r="G154" s="1">
+        <f t="shared" si="10"/>
+        <v>287.06820999999997</v>
+      </c>
+      <c r="H154" s="1">
+        <f t="shared" si="11"/>
+        <v>1993.26179</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E155" s="1">
+        <v>145.91999999999999</v>
+      </c>
+      <c r="F155" s="1">
+        <f t="shared" si="9"/>
+        <v>14.591999999999999</v>
+      </c>
+      <c r="G155" s="1">
+        <f t="shared" si="10"/>
+        <v>16.532736</v>
+      </c>
+      <c r="H155" s="1">
+        <f t="shared" si="11"/>
+        <v>114.79526399999997</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1321.25</v>
+      </c>
+      <c r="F156" s="1">
+        <f t="shared" si="9"/>
+        <v>132.125</v>
+      </c>
+      <c r="G156" s="1">
+        <f t="shared" si="10"/>
+        <v>149.69762499999999</v>
+      </c>
+      <c r="H156" s="1">
+        <f t="shared" si="11"/>
+        <v>1039.427375</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E157" s="1">
+        <v>949.12</v>
+      </c>
+      <c r="F157" s="1">
+        <f t="shared" si="9"/>
+        <v>94.912000000000006</v>
+      </c>
+      <c r="G157" s="1">
+        <f t="shared" si="10"/>
+        <v>107.535296</v>
+      </c>
+      <c r="H157" s="1">
+        <f t="shared" si="11"/>
+        <v>746.67270399999995</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E158" s="1">
+        <v>0</v>
+      </c>
+      <c r="F158" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G158" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H158" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E159" s="1">
+        <v>350.55</v>
+      </c>
+      <c r="F159" s="1">
+        <f t="shared" si="9"/>
+        <v>35.055</v>
+      </c>
+      <c r="G159" s="1">
+        <f t="shared" si="10"/>
+        <v>39.717314999999999</v>
+      </c>
+      <c r="H159" s="1">
+        <f t="shared" si="11"/>
+        <v>275.77768500000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E160" s="1">
+        <v>2937.66</v>
+      </c>
+      <c r="F160" s="1">
+        <f t="shared" si="9"/>
+        <v>293.76600000000002</v>
+      </c>
+      <c r="G160" s="1">
+        <f t="shared" si="10"/>
+        <v>332.83687799999996</v>
+      </c>
+      <c r="H160" s="1">
+        <f t="shared" si="11"/>
+        <v>2311.0571219999997</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D161" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E161" s="1">
+        <v>9253.1200000000008</v>
+      </c>
+      <c r="F161" s="1">
+        <f t="shared" si="9"/>
+        <v>925.31200000000013</v>
+      </c>
+      <c r="G161" s="1">
+        <f t="shared" si="10"/>
+        <v>1048.378496</v>
+      </c>
+      <c r="H161" s="1">
+        <f t="shared" si="11"/>
+        <v>7279.4295040000006</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E162" s="1">
+        <v>10187.52</v>
+      </c>
+      <c r="F162" s="1">
+        <f t="shared" si="9"/>
+        <v>1018.7520000000001</v>
+      </c>
+      <c r="G162" s="1">
+        <f t="shared" si="10"/>
+        <v>1154.2460160000001</v>
+      </c>
+      <c r="H162" s="1">
+        <f t="shared" si="11"/>
+        <v>8014.521984</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D163" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E163" s="1">
+        <v>3850.16</v>
+      </c>
+      <c r="F163" s="1">
+        <f t="shared" si="9"/>
+        <v>385.01600000000002</v>
+      </c>
+      <c r="G163" s="1">
+        <f t="shared" si="10"/>
+        <v>436.22312799999997</v>
+      </c>
+      <c r="H163" s="1">
+        <f t="shared" si="11"/>
+        <v>3028.9208719999997</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117" xr:uid="{EA5D708C-AB31-473E-9B9D-79F5ACDE382B}">
+  <autoFilter ref="A1:H148" xr:uid="{EA5D708C-AB31-473E-9B9D-79F5ACDE382B}">
     <filterColumn colId="3">
       <filters>
-        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
-        <dateGroupItem year="2025" dateTimeGrouping="year"/>
+        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
   </autoFilter>
